--- a/data/trending_integrated_20261027_15.xlsx
+++ b/data/trending_integrated_20261027_15.xlsx
@@ -578,10 +578,10 @@
         <v>-0.41</v>
       </c>
       <c r="E2" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F2" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G2" t="n">
         <v>92</v>
@@ -610,7 +610,7 @@
         <v>0.5</v>
       </c>
       <c r="O2" t="n">
-        <v>42009909580</v>
+        <v>42021655440</v>
       </c>
       <c r="P2" t="n">
         <v>28800</v>
@@ -702,7 +702,7 @@
         <v>4.28</v>
       </c>
       <c r="O3" t="n">
-        <v>18759931775</v>
+        <v>18767297565</v>
       </c>
       <c r="P3" t="n">
         <v>28600</v>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>9180</v>
+        <v>9105</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+29.30%</t>
+          <t>'+28.24%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="E4" t="n">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="F4" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="G4" t="n">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="H4" t="n">
         <v>2.12</v>
@@ -794,7 +794,7 @@
         <v>2.05</v>
       </c>
       <c r="O4" t="n">
-        <v>51338901140</v>
+        <v>53113492730</v>
       </c>
       <c r="P4" t="n">
         <v>29750</v>
@@ -854,13 +854,13 @@
         <v>0.12</v>
       </c>
       <c r="E5" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F5" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G5" t="n">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="H5" t="n">
         <v>0.3</v>
@@ -886,7 +886,7 @@
         <v>0.18</v>
       </c>
       <c r="O5" t="n">
-        <v>71838412065</v>
+        <v>72134688065</v>
       </c>
       <c r="P5" t="n">
         <v>62100</v>
@@ -935,11 +935,11 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1352500</v>
+        <v>1351000</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+6.08%</t>
+          <t>'+5.96%</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -949,10 +949,10 @@
         <v>800</v>
       </c>
       <c r="F6" t="n">
-        <v>446</v>
+        <v>453</v>
       </c>
       <c r="G6" t="n">
-        <v>1659</v>
+        <v>1668</v>
       </c>
       <c r="H6" t="n">
         <v>48.66</v>
@@ -978,7 +978,7 @@
         <v>48.69</v>
       </c>
       <c r="O6" t="n">
-        <v>3222931579500</v>
+        <v>3318450251500</v>
       </c>
       <c r="P6" t="n">
         <v>2987000</v>
@@ -994,16 +994,16 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>실적 발표 및 주주환원 발표에 대한 기대감이 높으며, 외국인 수급 유입이 관측됨. 일부에서는 150만, 200만 돌파 전망 제시.</t>
+          <t>실적 발표 및 주주환원 기대감에 따른 상승 전망. 외국인 수급 긍정적이나 일부 하락 예측 존재.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['실적', '주주환원', '외국인수급']</t>
+          <t>['실적', '주주환원', '전망']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1023,83 +1023,83 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>앤로보틱스</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>222250</v>
+        <v>2125</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+4.34%</t>
+          <t>'+4.42%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.01</v>
+        <v>-0.11</v>
       </c>
       <c r="E7" t="n">
-        <v>800</v>
+        <v>126</v>
       </c>
       <c r="F7" t="n">
-        <v>444</v>
+        <v>58</v>
       </c>
       <c r="G7" t="n">
-        <v>1413</v>
+        <v>286</v>
       </c>
       <c r="H7" t="n">
-        <v>46.1</v>
+        <v>4.89</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>213000</v>
+        <v>2035</v>
       </c>
       <c r="K7" t="n">
-        <v>222000</v>
+        <v>2035</v>
       </c>
       <c r="L7" t="n">
-        <v>225500</v>
+        <v>2300</v>
       </c>
       <c r="M7" t="n">
-        <v>220000</v>
+        <v>1953</v>
       </c>
       <c r="N7" t="n">
-        <v>46.11</v>
+        <v>5</v>
       </c>
       <c r="O7" t="n">
-        <v>2443490314250</v>
+        <v>52933620705</v>
       </c>
       <c r="P7" t="n">
-        <v>374500</v>
+        <v>4980</v>
       </c>
       <c r="Q7" t="n">
-        <v>94500</v>
+        <v>749</v>
       </c>
       <c r="R7" t="n">
-        <v>1197000</v>
+        <v>-35000</v>
       </c>
       <c r="S7" t="n">
-        <v>668000</v>
+        <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>실적 및 주주환원 발표 기대감에도 불구하고 외인 매도세가 관측되며 주가 상승폭이 제한적인 모습. 공매도 세력에 대한 언급 존재.</t>
+          <t>단기 급등 후 변동성 확대. 언론 보도 및 스마트 팩토리 관련 언급. 투자주의 종목 지정.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['실적', '주주환원', '외인매도']</t>
+          <t>['변동성', '스마트팩토리', '언론보도']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>138360</t>
         </is>
       </c>
     </row>
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>62300</v>
+        <v>62400</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+4.18%</t>
+          <t>'+4.35%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>0.05</v>
       </c>
       <c r="E8" t="n">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="F8" t="n">
         <v>101</v>
       </c>
       <c r="G8" t="n">
-        <v>961</v>
+        <v>969</v>
       </c>
       <c r="H8" t="n">
         <v>40.44</v>
@@ -1162,7 +1162,7 @@
         <v>40.39</v>
       </c>
       <c r="O8" t="n">
-        <v>256925215500</v>
+        <v>262206241600</v>
       </c>
       <c r="P8" t="n">
         <v>67300</v>
@@ -1207,70 +1207,70 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>앤로보틱스</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2105</v>
+        <v>222250</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+3.44%</t>
+          <t>'+4.34%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.11</v>
+        <v>-0.01</v>
       </c>
       <c r="E9" t="n">
-        <v>126</v>
+        <v>800</v>
       </c>
       <c r="F9" t="n">
-        <v>59</v>
+        <v>445</v>
       </c>
       <c r="G9" t="n">
-        <v>283</v>
+        <v>1383</v>
       </c>
       <c r="H9" t="n">
-        <v>4.89</v>
+        <v>46.1</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>2035</v>
+        <v>213000</v>
       </c>
       <c r="K9" t="n">
-        <v>2035</v>
+        <v>222000</v>
       </c>
       <c r="L9" t="n">
-        <v>2300</v>
+        <v>225500</v>
       </c>
       <c r="M9" t="n">
-        <v>1953</v>
+        <v>220000</v>
       </c>
       <c r="N9" t="n">
-        <v>5</v>
+        <v>46.11</v>
       </c>
       <c r="O9" t="n">
-        <v>52607621762</v>
+        <v>2482373989250</v>
       </c>
       <c r="P9" t="n">
-        <v>4980</v>
+        <v>374500</v>
       </c>
       <c r="Q9" t="n">
-        <v>749</v>
+        <v>94500</v>
       </c>
       <c r="R9" t="n">
-        <v>-35000</v>
+        <v>1197000</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>668000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>종가 관리 및 주가 흐름에 대한 긍정적 언급과 함께 삼성전자와의 연관성 언급. 변동성 수반 속 주가 상승 기대.</t>
+          <t>실적 및 주주환원 발표 예정, 일부 공매도 언급. 주가 변동성 및 외인 매매 동향 혼조.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
@@ -1279,11 +1279,11 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['종가관리', '주가흐름', '변동성']</t>
+          <t>['실적', '주주환원', '공매도']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>138360</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>13780</v>
+        <v>13735</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+2.99%</t>
+          <t>'+2.65%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F10" t="n">
         <v>54</v>
       </c>
       <c r="G10" t="n">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="H10" t="n">
         <v>2.82</v>
@@ -1346,7 +1346,7 @@
         <v>2.82</v>
       </c>
       <c r="O10" t="n">
-        <v>62595552975</v>
+        <v>63062990770</v>
       </c>
       <c r="P10" t="n">
         <v>31500</v>
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>14500</v>
+        <v>14510</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+1.97%</t>
+          <t>'+2.04%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>-0.01</v>
       </c>
       <c r="E11" t="n">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="F11" t="n">
         <v>67</v>
       </c>
       <c r="G11" t="n">
-        <v>535</v>
+        <v>543</v>
       </c>
       <c r="H11" t="n">
         <v>10.02</v>
@@ -1438,7 +1438,7 @@
         <v>10.03</v>
       </c>
       <c r="O11" t="n">
-        <v>42044293605</v>
+        <v>42762506665</v>
       </c>
       <c r="P11" t="n">
         <v>40350</v>
@@ -1483,184 +1483,184 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>루닛</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>16440</v>
+        <v>14830</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+0.86%</t>
+          <t>'+0.95%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.02</v>
+        <v>0.46</v>
       </c>
       <c r="E12" t="n">
-        <v>104</v>
+        <v>173</v>
       </c>
       <c r="F12" t="n">
-        <v>60</v>
+        <v>101</v>
       </c>
       <c r="G12" t="n">
-        <v>300</v>
+        <v>610</v>
       </c>
       <c r="H12" t="n">
-        <v>27.96</v>
+        <v>7.82</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>16300</v>
+        <v>14690</v>
       </c>
       <c r="K12" t="n">
-        <v>16410</v>
+        <v>14490</v>
       </c>
       <c r="L12" t="n">
-        <v>16770</v>
+        <v>15800</v>
       </c>
       <c r="M12" t="n">
-        <v>16270</v>
+        <v>14260</v>
       </c>
       <c r="N12" t="n">
-        <v>27.94</v>
+        <v>7.36</v>
       </c>
       <c r="O12" t="n">
-        <v>48079310685</v>
+        <v>85200234690</v>
       </c>
       <c r="P12" t="n">
-        <v>35350</v>
+        <v>49800</v>
       </c>
       <c r="Q12" t="n">
-        <v>16270</v>
+        <v>8180</v>
       </c>
       <c r="R12" t="n">
-        <v>21000</v>
+        <v>48000</v>
       </c>
       <c r="S12" t="n">
-        <v>-17000</v>
+        <v>125000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>외국인 및 기관 매수세 언급에도 불구하고 주가 부진 및 부정적 전망이 우세. 저가 인식 및 비관적 견해 다수.</t>
+          <t>해외 수출 및 신약 개발 활용 성공 사례 언급. AI 의료주 대장으로서의 성장성 및 확장성 부각.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['외국인 매수', '주가 부진', '부정적 전망']</t>
+          <t>['수출', '신약개발', 'AI의료']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>328130</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>루닛</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>14700</v>
+        <v>16400</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'+0.07%</t>
+          <t>'+0.61%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.46</v>
+        <v>0.02</v>
       </c>
       <c r="E13" t="n">
-        <v>171</v>
+        <v>107</v>
       </c>
       <c r="F13" t="n">
-        <v>99</v>
+        <v>61</v>
       </c>
       <c r="G13" t="n">
-        <v>602</v>
+        <v>308</v>
       </c>
       <c r="H13" t="n">
-        <v>7.82</v>
+        <v>27.96</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>14690</v>
+        <v>16300</v>
       </c>
       <c r="K13" t="n">
-        <v>14490</v>
+        <v>16410</v>
       </c>
       <c r="L13" t="n">
-        <v>15800</v>
+        <v>16770</v>
       </c>
       <c r="M13" t="n">
-        <v>14260</v>
+        <v>16270</v>
       </c>
       <c r="N13" t="n">
-        <v>7.36</v>
+        <v>27.94</v>
       </c>
       <c r="O13" t="n">
-        <v>84123129210</v>
+        <v>48804901095</v>
       </c>
       <c r="P13" t="n">
-        <v>49800</v>
+        <v>35350</v>
       </c>
       <c r="Q13" t="n">
-        <v>8180</v>
+        <v>16270</v>
       </c>
       <c r="R13" t="n">
-        <v>48000</v>
+        <v>21000</v>
       </c>
       <c r="S13" t="n">
-        <v>125000</v>
+        <v>-17000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>해외 수출 및 신약 개발 활용 성공 사례 언급. AI 의료주 대장으로서의 성장성 및 확장성 부각.</t>
+          <t>외국인 및 기관 매수세 언급에도 불구하고 주가 부진 및 부정적 전망이 우세. 저가 인식 및 비관적 견해 다수.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['수출', '신약개발', 'AI의료']</t>
+          <t>['외국인 매수', '주가 부진', '부정적 전망']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>328130</t>
+          <t>010140</t>
         </is>
       </c>
     </row>
@@ -1671,24 +1671,24 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>25900</v>
+        <v>25950</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-2.26%</t>
+          <t>'-2.08%</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>-0.07000000000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="F14" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G14" t="n">
-        <v>332</v>
+        <v>354</v>
       </c>
       <c r="H14" t="n">
         <v>12.32</v>
@@ -1714,7 +1714,7 @@
         <v>12.39</v>
       </c>
       <c r="O14" t="n">
-        <v>57316940925</v>
+        <v>59639153650</v>
       </c>
       <c r="P14" t="n">
         <v>59300</v>
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>34850</v>
+        <v>34950</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-4.52%</t>
+          <t>'-4.25%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>0.62</v>
       </c>
       <c r="E15" t="n">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="F15" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G15" t="n">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="H15" t="n">
         <v>8.65</v>
@@ -1806,7 +1806,7 @@
         <v>8.029999999999999</v>
       </c>
       <c r="O15" t="n">
-        <v>119297412050</v>
+        <v>120252242775</v>
       </c>
       <c r="P15" t="n">
         <v>126600</v>

--- a/data/trending_integrated_20261027_15.xlsx
+++ b/data/trending_integrated_20261027_15.xlsx
@@ -578,13 +578,13 @@
         <v>-0.41</v>
       </c>
       <c r="E2" t="n">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="F2" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G2" t="n">
-        <v>92</v>
+        <v>77</v>
       </c>
       <c r="H2" t="n">
         <v>0.09</v>
@@ -610,7 +610,7 @@
         <v>0.5</v>
       </c>
       <c r="O2" t="n">
-        <v>42021655440</v>
+        <v>42047632470</v>
       </c>
       <c r="P2" t="n">
         <v>28800</v>
@@ -670,13 +670,13 @@
         <v>-0.15</v>
       </c>
       <c r="E3" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F3" t="n">
         <v>65</v>
       </c>
       <c r="G3" t="n">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="H3" t="n">
         <v>4.13</v>
@@ -702,7 +702,7 @@
         <v>4.28</v>
       </c>
       <c r="O3" t="n">
-        <v>18767297565</v>
+        <v>18767553915</v>
       </c>
       <c r="P3" t="n">
         <v>28600</v>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>9105</v>
+        <v>9040</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+28.24%</t>
+          <t>'+27.32%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="E4" t="n">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="F4" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G4" t="n">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H4" t="n">
         <v>2.12</v>
@@ -794,7 +794,7 @@
         <v>2.05</v>
       </c>
       <c r="O4" t="n">
-        <v>53113492730</v>
+        <v>54528647065</v>
       </c>
       <c r="P4" t="n">
         <v>29750</v>
@@ -839,31 +839,31 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>브릴스</t>
+          <t>앤로보틱스</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>20300</v>
+        <v>2175</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+6.56%</t>
+          <t>'+6.88%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.12</v>
+        <v>-0.11</v>
       </c>
       <c r="E5" t="n">
-        <v>93</v>
+        <v>132</v>
       </c>
       <c r="F5" t="n">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="G5" t="n">
-        <v>175</v>
+        <v>300</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3</v>
+        <v>4.89</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -871,222 +871,222 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>19050</v>
+        <v>2035</v>
       </c>
       <c r="K5" t="n">
-        <v>19450</v>
+        <v>2035</v>
       </c>
       <c r="L5" t="n">
-        <v>22450</v>
+        <v>2300</v>
       </c>
       <c r="M5" t="n">
-        <v>18430</v>
+        <v>1953</v>
       </c>
       <c r="N5" t="n">
-        <v>0.18</v>
+        <v>5</v>
       </c>
       <c r="O5" t="n">
-        <v>72134688065</v>
+        <v>53957179025</v>
       </c>
       <c r="P5" t="n">
-        <v>62100</v>
+        <v>4980</v>
       </c>
       <c r="Q5" t="n">
-        <v>14600</v>
+        <v>749</v>
       </c>
       <c r="R5" t="n">
-        <v>32000</v>
+        <v>-35000</v>
       </c>
       <c r="S5" t="n">
-        <v>-1000</v>
+        <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>로봇 기업으로 빅웨이브 및 흑자 기업임을 언급. 단기 변동성 및 기술적 분석 기반 상승 여력 논의.</t>
+          <t>삼성전자 연계 언급과 함께 상승 기대감. 변동성 높은 장세 속 종가 관리 및 흐름 긍정적.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['로봇', '흑자기업', '기술적 분석']</t>
+          <t>['스마트 팩토리', '변동성', '연계']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>468670</t>
+          <t>138360</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>브릴스</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1351000</v>
+        <v>20300</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+5.96%</t>
+          <t>'+6.56%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-0.03</v>
+        <v>0.12</v>
       </c>
       <c r="E6" t="n">
-        <v>800</v>
+        <v>95</v>
       </c>
       <c r="F6" t="n">
-        <v>453</v>
+        <v>55</v>
       </c>
       <c r="G6" t="n">
-        <v>1668</v>
+        <v>175</v>
       </c>
       <c r="H6" t="n">
-        <v>48.66</v>
+        <v>0.3</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>1275000</v>
+        <v>19050</v>
       </c>
       <c r="K6" t="n">
-        <v>1346000</v>
+        <v>19450</v>
       </c>
       <c r="L6" t="n">
-        <v>1381000</v>
+        <v>22450</v>
       </c>
       <c r="M6" t="n">
-        <v>1336000</v>
+        <v>18430</v>
       </c>
       <c r="N6" t="n">
-        <v>48.69</v>
+        <v>0.18</v>
       </c>
       <c r="O6" t="n">
-        <v>3318450251500</v>
+        <v>72688032065</v>
       </c>
       <c r="P6" t="n">
-        <v>2987000</v>
+        <v>62100</v>
       </c>
       <c r="Q6" t="n">
-        <v>501000</v>
+        <v>14600</v>
       </c>
       <c r="R6" t="n">
-        <v>28000</v>
+        <v>32000</v>
       </c>
       <c r="S6" t="n">
-        <v>168000</v>
+        <v>-1000</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>실적 발표 및 주주환원 기대감에 따른 상승 전망. 외국인 수급 긍정적이나 일부 하락 예측 존재.</t>
+          <t>로봇 기업으로 빅웨이브 및 흑자 기업임을 언급. 단기 변동성 및 기술적 분석 기반 상승 여력 논의.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['실적', '주주환원', '전망']</t>
+          <t>['로봇', '흑자기업', '기술적 분석']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>468670</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>앤로보틱스</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2125</v>
+        <v>1341000</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+4.42%</t>
+          <t>'+5.18%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.11</v>
+        <v>-0.03</v>
       </c>
       <c r="E7" t="n">
-        <v>126</v>
+        <v>800</v>
       </c>
       <c r="F7" t="n">
-        <v>58</v>
+        <v>448</v>
       </c>
       <c r="G7" t="n">
-        <v>286</v>
+        <v>1689</v>
       </c>
       <c r="H7" t="n">
-        <v>4.89</v>
+        <v>48.66</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>2035</v>
+        <v>1275000</v>
       </c>
       <c r="K7" t="n">
-        <v>2035</v>
+        <v>1346000</v>
       </c>
       <c r="L7" t="n">
-        <v>2300</v>
+        <v>1381000</v>
       </c>
       <c r="M7" t="n">
-        <v>1953</v>
+        <v>1336000</v>
       </c>
       <c r="N7" t="n">
-        <v>5</v>
+        <v>48.69</v>
       </c>
       <c r="O7" t="n">
-        <v>52933620705</v>
+        <v>3430198826000</v>
       </c>
       <c r="P7" t="n">
-        <v>4980</v>
+        <v>2987000</v>
       </c>
       <c r="Q7" t="n">
-        <v>749</v>
+        <v>501000</v>
       </c>
       <c r="R7" t="n">
-        <v>-35000</v>
+        <v>28000</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>168000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>단기 급등 후 변동성 확대. 언론 보도 및 스마트 팩토리 관련 언급. 투자주의 종목 지정.</t>
+          <t>추가 주주환원 및 어닝 서프라이즈 실적 발표 기대감. 140만원 탈환 및 상승 전망.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
@@ -1095,11 +1095,11 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['변동성', '스마트팩토리', '언론보도']</t>
+          <t>['주주환원', '실적', '어닝 서프라이즈']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,38 +1108,38 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>138360</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>삼성E&amp;A</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>62400</v>
+        <v>221000</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+4.35%</t>
+          <t>'+3.76%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.05</v>
+        <v>-0.01</v>
       </c>
       <c r="E8" t="n">
-        <v>161</v>
+        <v>800</v>
       </c>
       <c r="F8" t="n">
-        <v>101</v>
+        <v>438</v>
       </c>
       <c r="G8" t="n">
-        <v>969</v>
+        <v>1374</v>
       </c>
       <c r="H8" t="n">
-        <v>40.44</v>
+        <v>46.1</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1147,51 +1147,51 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>59800</v>
+        <v>213000</v>
       </c>
       <c r="K8" t="n">
-        <v>60700</v>
+        <v>222000</v>
       </c>
       <c r="L8" t="n">
-        <v>63900</v>
+        <v>225500</v>
       </c>
       <c r="M8" t="n">
-        <v>60100</v>
+        <v>220000</v>
       </c>
       <c r="N8" t="n">
-        <v>40.39</v>
+        <v>46.11</v>
       </c>
       <c r="O8" t="n">
-        <v>262206241600</v>
+        <v>2562621829250</v>
       </c>
       <c r="P8" t="n">
-        <v>67300</v>
+        <v>374500</v>
       </c>
       <c r="Q8" t="n">
-        <v>23150</v>
+        <v>94500</v>
       </c>
       <c r="R8" t="n">
-        <v>406000</v>
+        <v>1197000</v>
       </c>
       <c r="S8" t="n">
-        <v>-25000</v>
+        <v>668000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>삼성E&amp;A, 중동 지역 수주 기대감 및 그룹사 투자 모멘텀에 따른 주가 상승 전망. MSCI 편입 기대감과 함께 저평가 매력이 부각되며 긍정적 투심 형성.</t>
+          <t>트럼프 외교 관련 언급과 함께 30만원 재진입 기대감. 실적 및 주주환원 발표 예정.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['중동 수주', 'MSCI 편입', '저평가']</t>
+          <t>['주주환원', '실적', '외교']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,38 +1200,38 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>028050</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>삼성E&amp;A</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>222250</v>
+        <v>62000</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+4.34%</t>
+          <t>'+3.68%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.01</v>
+        <v>0.05</v>
       </c>
       <c r="E9" t="n">
-        <v>800</v>
+        <v>165</v>
       </c>
       <c r="F9" t="n">
-        <v>445</v>
+        <v>104</v>
       </c>
       <c r="G9" t="n">
-        <v>1383</v>
+        <v>983</v>
       </c>
       <c r="H9" t="n">
-        <v>46.1</v>
+        <v>40.44</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1239,51 +1239,51 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>213000</v>
+        <v>59800</v>
       </c>
       <c r="K9" t="n">
-        <v>222000</v>
+        <v>60700</v>
       </c>
       <c r="L9" t="n">
-        <v>225500</v>
+        <v>63900</v>
       </c>
       <c r="M9" t="n">
-        <v>220000</v>
+        <v>60100</v>
       </c>
       <c r="N9" t="n">
-        <v>46.11</v>
+        <v>40.39</v>
       </c>
       <c r="O9" t="n">
-        <v>2482373989250</v>
+        <v>269123660200</v>
       </c>
       <c r="P9" t="n">
-        <v>374500</v>
+        <v>67300</v>
       </c>
       <c r="Q9" t="n">
-        <v>94500</v>
+        <v>23150</v>
       </c>
       <c r="R9" t="n">
-        <v>1197000</v>
+        <v>406000</v>
       </c>
       <c r="S9" t="n">
-        <v>668000</v>
+        <v>-25000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>실적 및 주주환원 발표 예정, 일부 공매도 언급. 주가 변동성 및 외인 매매 동향 혼조.</t>
+          <t>중동 정세 및 삼성그룹 연계 투자 언급. MSCI 종목 편입 기대감과 함께 7만원 목표.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['실적', '주주환원', '공매도']</t>
+          <t>['MSCI', '중동', '저평가']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>028050</t>
         </is>
       </c>
     </row>
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>13735</v>
+        <v>13700</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+2.65%</t>
+          <t>'+2.39%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="F10" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G10" t="n">
-        <v>418</v>
+        <v>426</v>
       </c>
       <c r="H10" t="n">
         <v>2.82</v>
@@ -1346,7 +1346,7 @@
         <v>2.82</v>
       </c>
       <c r="O10" t="n">
-        <v>63062990770</v>
+        <v>63885472580</v>
       </c>
       <c r="P10" t="n">
         <v>31500</v>
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>14510</v>
+        <v>14430</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+2.04%</t>
+          <t>'+1.48%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>-0.01</v>
       </c>
       <c r="E11" t="n">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="F11" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G11" t="n">
-        <v>543</v>
+        <v>549</v>
       </c>
       <c r="H11" t="n">
         <v>10.02</v>
@@ -1438,7 +1438,7 @@
         <v>10.03</v>
       </c>
       <c r="O11" t="n">
-        <v>42762506665</v>
+        <v>43779873180</v>
       </c>
       <c r="P11" t="n">
         <v>40350</v>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>223% 영업이익 증가라는 긍정적인 실적 발표가 있었으나, 주가 반등이 미미하고 도배글 신고가 잦아 투자 심리가 혼재.</t>
+          <t>영업이익 223% 증가 실적 발표. AI 수혜주로서의 기대감과 함께 상승.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
@@ -1463,7 +1463,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['영업이익', '실적발표', '반등']</t>
+          <t>['영업이익', '실적', 'AI']</t>
         </is>
       </c>
       <c r="X11" t="n">
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>14830</v>
+        <v>14730</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+0.95%</t>
+          <t>'+0.27%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>0.46</v>
       </c>
       <c r="E12" t="n">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="F12" t="n">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="G12" t="n">
-        <v>610</v>
+        <v>620</v>
       </c>
       <c r="H12" t="n">
         <v>7.82</v>
@@ -1530,7 +1530,7 @@
         <v>7.36</v>
       </c>
       <c r="O12" t="n">
-        <v>85200234690</v>
+        <v>86005363345</v>
       </c>
       <c r="P12" t="n">
         <v>49800</v>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>해외 수출 및 신약 개발 활용 성공 사례 언급. AI 의료주 대장으로서의 성장성 및 확장성 부각.</t>
+          <t>해외 수출 및 신약 개발 활용 기반 성장성 부각. AI 의료 분야 경쟁력 강화 및 해외 인수합병 기대.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
@@ -1555,7 +1555,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['수출', '신약개발', 'AI의료']</t>
+          <t>['AI 의료', '신약개발', '해외수출']</t>
         </is>
       </c>
       <c r="X12" t="n">
@@ -1579,24 +1579,24 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>16400</v>
+        <v>16330</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'+0.61%</t>
+          <t>'+0.18%</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>0.02</v>
       </c>
       <c r="E13" t="n">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="F13" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G13" t="n">
-        <v>308</v>
+        <v>319</v>
       </c>
       <c r="H13" t="n">
         <v>27.96</v>
@@ -1622,7 +1622,7 @@
         <v>27.94</v>
       </c>
       <c r="O13" t="n">
-        <v>48804901095</v>
+        <v>50553504640</v>
       </c>
       <c r="P13" t="n">
         <v>35350</v>
@@ -1671,11 +1671,11 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>25950</v>
+        <v>25850</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-2.08%</t>
+          <t>'-2.45%</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -1685,7 +1685,7 @@
         <v>107</v>
       </c>
       <c r="F14" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="G14" t="n">
         <v>354</v>
@@ -1714,7 +1714,7 @@
         <v>12.39</v>
       </c>
       <c r="O14" t="n">
-        <v>59639153650</v>
+        <v>61984639275</v>
       </c>
       <c r="P14" t="n">
         <v>59300</v>
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>34950</v>
+        <v>34500</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-4.25%</t>
+          <t>'-5.48%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>0.62</v>
       </c>
       <c r="E15" t="n">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="F15" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G15" t="n">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H15" t="n">
         <v>8.65</v>
@@ -1806,7 +1806,7 @@
         <v>8.029999999999999</v>
       </c>
       <c r="O15" t="n">
-        <v>120252242775</v>
+        <v>121676722525</v>
       </c>
       <c r="P15" t="n">
         <v>126600</v>

--- a/data/trending_integrated_20261027_15.xlsx
+++ b/data/trending_integrated_20261027_15.xlsx
@@ -584,7 +584,7 @@
         <v>40</v>
       </c>
       <c r="G2" t="n">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="H2" t="n">
         <v>0.09</v>
@@ -610,7 +610,7 @@
         <v>0.5</v>
       </c>
       <c r="O2" t="n">
-        <v>42047632470</v>
+        <v>42054233580</v>
       </c>
       <c r="P2" t="n">
         <v>28800</v>
@@ -673,10 +673,10 @@
         <v>103</v>
       </c>
       <c r="F3" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G3" t="n">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="H3" t="n">
         <v>4.13</v>
@@ -702,7 +702,7 @@
         <v>4.28</v>
       </c>
       <c r="O3" t="n">
-        <v>18767553915</v>
+        <v>18780149245</v>
       </c>
       <c r="P3" t="n">
         <v>28600</v>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>9040</v>
+        <v>9000</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+27.32%</t>
+          <t>'+26.76%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="E4" t="n">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="F4" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="G4" t="n">
-        <v>177</v>
+        <v>193</v>
       </c>
       <c r="H4" t="n">
         <v>2.12</v>
@@ -794,7 +794,7 @@
         <v>2.05</v>
       </c>
       <c r="O4" t="n">
-        <v>54528647065</v>
+        <v>54937823065</v>
       </c>
       <c r="P4" t="n">
         <v>29750</v>
@@ -839,31 +839,31 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>앤로보틱스</t>
+          <t>브릴스</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2175</v>
+        <v>20450</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+6.88%</t>
+          <t>'+7.35%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-0.11</v>
+        <v>0.12</v>
       </c>
       <c r="E5" t="n">
-        <v>132</v>
+        <v>94</v>
       </c>
       <c r="F5" t="n">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="G5" t="n">
-        <v>300</v>
+        <v>184</v>
       </c>
       <c r="H5" t="n">
-        <v>4.89</v>
+        <v>0.3</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -871,91 +871,91 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>2035</v>
+        <v>19050</v>
       </c>
       <c r="K5" t="n">
-        <v>2035</v>
+        <v>19450</v>
       </c>
       <c r="L5" t="n">
-        <v>2300</v>
+        <v>22450</v>
       </c>
       <c r="M5" t="n">
-        <v>1953</v>
+        <v>18430</v>
       </c>
       <c r="N5" t="n">
-        <v>5</v>
+        <v>0.18</v>
       </c>
       <c r="O5" t="n">
-        <v>53957179025</v>
+        <v>72996561215</v>
       </c>
       <c r="P5" t="n">
-        <v>4980</v>
+        <v>62100</v>
       </c>
       <c r="Q5" t="n">
-        <v>749</v>
+        <v>14600</v>
       </c>
       <c r="R5" t="n">
-        <v>-35000</v>
+        <v>32000</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>-1000</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>삼성전자 연계 언급과 함께 상승 기대감. 변동성 높은 장세 속 종가 관리 및 흐름 긍정적.</t>
+          <t>로봇 기업으로 빅웨이브 및 흑자 기업임을 언급. 단기 변동성 및 기술적 분석 기반 상승 여력 논의.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['스마트 팩토리', '변동성', '연계']</t>
+          <t>['로봇', '흑자기업', '기술적 분석']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>138360</t>
+          <t>468670</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>브릴스</t>
+          <t>앤로보틱스</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>20300</v>
+        <v>2170</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+6.56%</t>
+          <t>'+6.63%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.12</v>
+        <v>-0.11</v>
       </c>
       <c r="E6" t="n">
-        <v>95</v>
+        <v>132</v>
       </c>
       <c r="F6" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="G6" t="n">
-        <v>175</v>
+        <v>299</v>
       </c>
       <c r="H6" t="n">
-        <v>0.3</v>
+        <v>4.89</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -963,60 +963,60 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>19050</v>
+        <v>2035</v>
       </c>
       <c r="K6" t="n">
-        <v>19450</v>
+        <v>2035</v>
       </c>
       <c r="L6" t="n">
-        <v>22450</v>
+        <v>2300</v>
       </c>
       <c r="M6" t="n">
-        <v>18430</v>
+        <v>1953</v>
       </c>
       <c r="N6" t="n">
-        <v>0.18</v>
+        <v>5</v>
       </c>
       <c r="O6" t="n">
-        <v>72688032065</v>
+        <v>54169934505</v>
       </c>
       <c r="P6" t="n">
-        <v>62100</v>
+        <v>4980</v>
       </c>
       <c r="Q6" t="n">
-        <v>14600</v>
+        <v>749</v>
       </c>
       <c r="R6" t="n">
-        <v>32000</v>
+        <v>-35000</v>
       </c>
       <c r="S6" t="n">
-        <v>-1000</v>
+        <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>로봇 기업으로 빅웨이브 및 흑자 기업임을 언급. 단기 변동성 및 기술적 분석 기반 상승 여력 논의.</t>
+          <t>삼성전자 연계 가능성 언급과 함께 변동성 확대. 장막판 페이크 상승 및 투자 주의 예고.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['로봇', '흑자기업', '기술적 분석']</t>
+          <t>['변동성', '삼성', '투자주의']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>468670</t>
+          <t>138360</t>
         </is>
       </c>
     </row>
@@ -1041,10 +1041,10 @@
         <v>800</v>
       </c>
       <c r="F7" t="n">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="G7" t="n">
-        <v>1689</v>
+        <v>1734</v>
       </c>
       <c r="H7" t="n">
         <v>48.66</v>
@@ -1070,7 +1070,7 @@
         <v>48.69</v>
       </c>
       <c r="O7" t="n">
-        <v>3430198826000</v>
+        <v>3838637924000</v>
       </c>
       <c r="P7" t="n">
         <v>2987000</v>
@@ -1086,16 +1086,16 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>추가 주주환원 및 어닝 서프라이즈 실적 발표 기대감. 140만원 탈환 및 상승 전망.</t>
+          <t>주주환원 및 실적 발표 기대감에 따른 상승 전망. 외국인 및 기관 매수세 확인.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['주주환원', '실적', '어닝 서프라이즈']</t>
+          <t>['주주환원', '실적', '외국인']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1119,11 +1119,11 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>221000</v>
+        <v>222000</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+3.76%</t>
+          <t>'+4.23%</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -1133,10 +1133,10 @@
         <v>800</v>
       </c>
       <c r="F8" t="n">
-        <v>438</v>
+        <v>434</v>
       </c>
       <c r="G8" t="n">
-        <v>1374</v>
+        <v>1388</v>
       </c>
       <c r="H8" t="n">
         <v>46.1</v>
@@ -1162,7 +1162,7 @@
         <v>46.11</v>
       </c>
       <c r="O8" t="n">
-        <v>2562621829250</v>
+        <v>2970311953250</v>
       </c>
       <c r="P8" t="n">
         <v>374500</v>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>트럼프 외교 관련 언급과 함께 30만원 재진입 기대감. 실적 및 주주환원 발표 예정.</t>
+          <t>대통령 외교 일정 언급과 함께 주주환원 발표 기대감. 다만, 외인 매도 및 주가 변동성으로 인한 혼조세.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['주주환원', '실적', '외교']</t>
+          <t>['주주환원', '외국인', '실적']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>62000</v>
+        <v>62200</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+3.68%</t>
+          <t>'+4.01%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>0.05</v>
       </c>
       <c r="E9" t="n">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F9" t="n">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="G9" t="n">
-        <v>983</v>
+        <v>971</v>
       </c>
       <c r="H9" t="n">
         <v>40.44</v>
@@ -1254,7 +1254,7 @@
         <v>40.39</v>
       </c>
       <c r="O9" t="n">
-        <v>269123660200</v>
+        <v>284405889200</v>
       </c>
       <c r="P9" t="n">
         <v>67300</v>
@@ -1270,16 +1270,16 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>중동 정세 및 삼성그룹 연계 투자 언급. MSCI 종목 편입 기대감과 함께 7만원 목표.</t>
+          <t>중동 사태 및 그룹사 투자 관련 언급. MSCI 편입 기대감과 수주 공시 가능성으로 인한 긍정적 전망.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['MSCI', '중동', '저평가']</t>
+          <t>['중동', 'MSCI', '수주']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1320,7 +1320,7 @@
         <v>55</v>
       </c>
       <c r="G10" t="n">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="H10" t="n">
         <v>2.82</v>
@@ -1346,7 +1346,7 @@
         <v>2.82</v>
       </c>
       <c r="O10" t="n">
-        <v>63885472580</v>
+        <v>64059695480</v>
       </c>
       <c r="P10" t="n">
         <v>31500</v>
@@ -1395,11 +1395,11 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>14430</v>
+        <v>14450</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+1.48%</t>
+          <t>'+1.62%</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -1412,7 +1412,7 @@
         <v>66</v>
       </c>
       <c r="G11" t="n">
-        <v>549</v>
+        <v>556</v>
       </c>
       <c r="H11" t="n">
         <v>10.02</v>
@@ -1438,7 +1438,7 @@
         <v>10.03</v>
       </c>
       <c r="O11" t="n">
-        <v>43779873180</v>
+        <v>44732070380</v>
       </c>
       <c r="P11" t="n">
         <v>40350</v>
@@ -1483,184 +1483,184 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>루닛</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>14730</v>
+        <v>16390</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+0.27%</t>
+          <t>'+0.55%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.46</v>
+        <v>0.02</v>
       </c>
       <c r="E12" t="n">
-        <v>179</v>
+        <v>114</v>
       </c>
       <c r="F12" t="n">
-        <v>104</v>
+        <v>64</v>
       </c>
       <c r="G12" t="n">
-        <v>620</v>
+        <v>351</v>
       </c>
       <c r="H12" t="n">
-        <v>7.82</v>
+        <v>27.96</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>14690</v>
+        <v>16300</v>
       </c>
       <c r="K12" t="n">
-        <v>14490</v>
+        <v>16410</v>
       </c>
       <c r="L12" t="n">
-        <v>15800</v>
+        <v>16770</v>
       </c>
       <c r="M12" t="n">
-        <v>14260</v>
+        <v>16270</v>
       </c>
       <c r="N12" t="n">
-        <v>7.36</v>
+        <v>27.94</v>
       </c>
       <c r="O12" t="n">
-        <v>86005363345</v>
+        <v>53929221820</v>
       </c>
       <c r="P12" t="n">
-        <v>49800</v>
+        <v>35350</v>
       </c>
       <c r="Q12" t="n">
-        <v>8180</v>
+        <v>16270</v>
       </c>
       <c r="R12" t="n">
-        <v>48000</v>
+        <v>21000</v>
       </c>
       <c r="S12" t="n">
-        <v>125000</v>
+        <v>-17000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>해외 수출 및 신약 개발 활용 기반 성장성 부각. AI 의료 분야 경쟁력 강화 및 해외 인수합병 기대.</t>
+          <t>외국인 및 기관 매수세 언급에도 불구하고 주가 부진 및 부정적 전망이 우세. 저가 인식 및 비관적 견해 다수.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['AI 의료', '신약개발', '해외수출']</t>
+          <t>['외국인 매수', '주가 부진', '부정적 전망']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>328130</t>
+          <t>010140</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>루닛</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>16330</v>
+        <v>14650</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'+0.18%</t>
+          <t>'-0.27%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.02</v>
+        <v>0.46</v>
       </c>
       <c r="E13" t="n">
-        <v>110</v>
+        <v>180</v>
       </c>
       <c r="F13" t="n">
-        <v>62</v>
+        <v>105</v>
       </c>
       <c r="G13" t="n">
-        <v>319</v>
+        <v>636</v>
       </c>
       <c r="H13" t="n">
-        <v>27.96</v>
+        <v>7.82</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>16300</v>
+        <v>14690</v>
       </c>
       <c r="K13" t="n">
-        <v>16410</v>
+        <v>14490</v>
       </c>
       <c r="L13" t="n">
-        <v>16770</v>
+        <v>15800</v>
       </c>
       <c r="M13" t="n">
-        <v>16270</v>
+        <v>14260</v>
       </c>
       <c r="N13" t="n">
-        <v>27.94</v>
+        <v>7.36</v>
       </c>
       <c r="O13" t="n">
-        <v>50553504640</v>
+        <v>86921999195</v>
       </c>
       <c r="P13" t="n">
-        <v>35350</v>
+        <v>49800</v>
       </c>
       <c r="Q13" t="n">
-        <v>16270</v>
+        <v>8180</v>
       </c>
       <c r="R13" t="n">
-        <v>21000</v>
+        <v>48000</v>
       </c>
       <c r="S13" t="n">
-        <v>-17000</v>
+        <v>125000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>외국인 및 기관 매수세 언급에도 불구하고 주가 부진 및 부정적 전망이 우세. 저가 인식 및 비관적 견해 다수.</t>
+          <t>해외 수출 및 신약 개발 활용에 따른 성장성 기대. AI 신약 개발 플랫폼 경쟁력 부각.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['외국인 매수', '주가 부진', '부정적 전망']</t>
+          <t>['AI', '신약개발', '수출']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>328130</t>
         </is>
       </c>
     </row>
@@ -1682,13 +1682,13 @@
         <v>-0.07000000000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="F14" t="n">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="G14" t="n">
-        <v>354</v>
+        <v>389</v>
       </c>
       <c r="H14" t="n">
         <v>12.32</v>
@@ -1714,7 +1714,7 @@
         <v>12.39</v>
       </c>
       <c r="O14" t="n">
-        <v>61984639275</v>
+        <v>62850743525</v>
       </c>
       <c r="P14" t="n">
         <v>59300</v>
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>34500</v>
+        <v>34750</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-5.48%</t>
+          <t>'-4.79%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>0.62</v>
       </c>
       <c r="E15" t="n">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="F15" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="G15" t="n">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="H15" t="n">
         <v>8.65</v>
@@ -1806,7 +1806,7 @@
         <v>8.029999999999999</v>
       </c>
       <c r="O15" t="n">
-        <v>121676722525</v>
+        <v>122244398525</v>
       </c>
       <c r="P15" t="n">
         <v>126600</v>
@@ -1822,16 +1822,16 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>실적 호조에도 불구하고 주가 하락 및 개인 물량 던지기 현상 지속. 금감원 및 정부의 시장 개입 촉구. 외인 매도세 관측.</t>
+          <t>실적 개선에도 불구하고 주가 하락 및 외인 매도세 지속. 정부의 시장 관심 촉구.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['실적', '주가하락', '외인매도']</t>
+          <t>['실적', '외국인', '하락']</t>
         </is>
       </c>
       <c r="X15" t="n">

--- a/data/trending_integrated_20261027_15.xlsx
+++ b/data/trending_integrated_20261027_15.xlsx
@@ -578,10 +578,10 @@
         <v>-0.41</v>
       </c>
       <c r="E2" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F2" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G2" t="n">
         <v>81</v>
@@ -676,7 +676,7 @@
         <v>66</v>
       </c>
       <c r="G3" t="n">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="H3" t="n">
         <v>4.13</v>
@@ -702,7 +702,7 @@
         <v>4.28</v>
       </c>
       <c r="O3" t="n">
-        <v>18780149245</v>
+        <v>18780371415</v>
       </c>
       <c r="P3" t="n">
         <v>28600</v>
@@ -762,13 +762,13 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="E4" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F4" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="G4" t="n">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="H4" t="n">
         <v>2.12</v>
@@ -794,7 +794,7 @@
         <v>2.05</v>
       </c>
       <c r="O4" t="n">
-        <v>54937823065</v>
+        <v>54949136065</v>
       </c>
       <c r="P4" t="n">
         <v>29750</v>
@@ -854,13 +854,13 @@
         <v>0.12</v>
       </c>
       <c r="E5" t="n">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="F5" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="G5" t="n">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="H5" t="n">
         <v>0.3</v>
@@ -886,7 +886,7 @@
         <v>0.18</v>
       </c>
       <c r="O5" t="n">
-        <v>72996561215</v>
+        <v>73001857765</v>
       </c>
       <c r="P5" t="n">
         <v>62100</v>
@@ -946,13 +946,13 @@
         <v>-0.11</v>
       </c>
       <c r="E6" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F6" t="n">
         <v>59</v>
       </c>
       <c r="G6" t="n">
-        <v>299</v>
+        <v>313</v>
       </c>
       <c r="H6" t="n">
         <v>4.89</v>
@@ -978,7 +978,7 @@
         <v>5</v>
       </c>
       <c r="O6" t="n">
-        <v>54169934505</v>
+        <v>54186116195</v>
       </c>
       <c r="P6" t="n">
         <v>4980</v>
@@ -994,16 +994,16 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>삼성전자 연계 가능성 언급과 함께 변동성 확대. 장막판 페이크 상승 및 투자 주의 예고.</t>
+          <t>종가 관리 및 긍정적인 흐름에 대한 기대감이 있으나, 삼성과의 연관성 및 투자 주의 예고 등 불확실성 요소가 존재함. 로봇 관련 테마로 언급됨.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['변동성', '삼성', '투자주의']</t>
+          <t>['로봇', '종가관리', '테마']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1044,7 +1044,7 @@
         <v>445</v>
       </c>
       <c r="G7" t="n">
-        <v>1734</v>
+        <v>1730</v>
       </c>
       <c r="H7" t="n">
         <v>48.66</v>
@@ -1070,7 +1070,7 @@
         <v>48.69</v>
       </c>
       <c r="O7" t="n">
-        <v>3838637924000</v>
+        <v>3838662062000</v>
       </c>
       <c r="P7" t="n">
         <v>2987000</v>
@@ -1086,16 +1086,16 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>주주환원 및 실적 발표 기대감에 따른 상승 전망. 외국인 및 기관 매수세 확인.</t>
+          <t>추가 주주환원 및 어닝 서프라이즈 실적 발표에 대한 기대감이 높으며, 랠리 시작 및 140만 탈환에 대한 기대가 있음. 다만, 외국인 수급 변동성이 존재함.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['주주환원', '실적', '외국인']</t>
+          <t>['주주환원', '실적', '기대감']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1133,10 +1133,10 @@
         <v>800</v>
       </c>
       <c r="F8" t="n">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="G8" t="n">
-        <v>1388</v>
+        <v>1402</v>
       </c>
       <c r="H8" t="n">
         <v>46.1</v>
@@ -1162,7 +1162,7 @@
         <v>46.11</v>
       </c>
       <c r="O8" t="n">
-        <v>2970311953250</v>
+        <v>2972286865250</v>
       </c>
       <c r="P8" t="n">
         <v>374500</v>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>대통령 외교 일정 언급과 함께 주주환원 발표 기대감. 다만, 외인 매도 및 주가 변동성으로 인한 혼조세.</t>
+          <t>실적 및 주주환원 발표 기대감 속에서 변동성 장세를 보이며, 외인 매도세가 관찰됨. 전반적으로 긍정적인 기대감이 있으나 구체적인 근거는 부족함.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['주주환원', '외국인', '실적']</t>
+          <t>['실적', '주주환원', '외인']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1222,13 +1222,13 @@
         <v>0.05</v>
       </c>
       <c r="E9" t="n">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="F9" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="G9" t="n">
-        <v>971</v>
+        <v>999</v>
       </c>
       <c r="H9" t="n">
         <v>40.44</v>
@@ -1254,7 +1254,7 @@
         <v>40.39</v>
       </c>
       <c r="O9" t="n">
-        <v>284405889200</v>
+        <v>284442649400</v>
       </c>
       <c r="P9" t="n">
         <v>67300</v>
@@ -1314,13 +1314,13 @@
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F10" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G10" t="n">
-        <v>430</v>
+        <v>442</v>
       </c>
       <c r="H10" t="n">
         <v>2.82</v>
@@ -1346,7 +1346,7 @@
         <v>2.82</v>
       </c>
       <c r="O10" t="n">
-        <v>64059695480</v>
+        <v>64069244380</v>
       </c>
       <c r="P10" t="n">
         <v>31500</v>
@@ -1406,13 +1406,13 @@
         <v>-0.01</v>
       </c>
       <c r="E11" t="n">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F11" t="n">
         <v>66</v>
       </c>
       <c r="G11" t="n">
-        <v>556</v>
+        <v>562</v>
       </c>
       <c r="H11" t="n">
         <v>10.02</v>
@@ -1438,7 +1438,7 @@
         <v>10.03</v>
       </c>
       <c r="O11" t="n">
-        <v>44732070380</v>
+        <v>44741043830</v>
       </c>
       <c r="P11" t="n">
         <v>40350</v>
@@ -1498,13 +1498,13 @@
         <v>0.02</v>
       </c>
       <c r="E12" t="n">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="F12" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="G12" t="n">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="H12" t="n">
         <v>27.96</v>
@@ -1530,7 +1530,7 @@
         <v>27.94</v>
       </c>
       <c r="O12" t="n">
-        <v>53929221820</v>
+        <v>53929680740</v>
       </c>
       <c r="P12" t="n">
         <v>35350</v>
@@ -1596,7 +1596,7 @@
         <v>105</v>
       </c>
       <c r="G13" t="n">
-        <v>636</v>
+        <v>649</v>
       </c>
       <c r="H13" t="n">
         <v>7.82</v>
@@ -1622,7 +1622,7 @@
         <v>7.36</v>
       </c>
       <c r="O13" t="n">
-        <v>86921999195</v>
+        <v>86936868945</v>
       </c>
       <c r="P13" t="n">
         <v>49800</v>
@@ -1682,13 +1682,13 @@
         <v>-0.07000000000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="F14" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G14" t="n">
-        <v>389</v>
+        <v>414</v>
       </c>
       <c r="H14" t="n">
         <v>12.32</v>
@@ -1714,7 +1714,7 @@
         <v>12.39</v>
       </c>
       <c r="O14" t="n">
-        <v>62850743525</v>
+        <v>62906036675</v>
       </c>
       <c r="P14" t="n">
         <v>59300</v>
@@ -1774,13 +1774,13 @@
         <v>0.62</v>
       </c>
       <c r="E15" t="n">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="F15" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G15" t="n">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H15" t="n">
         <v>8.65</v>
@@ -1806,7 +1806,7 @@
         <v>8.029999999999999</v>
       </c>
       <c r="O15" t="n">
-        <v>122244398525</v>
+        <v>122266360525</v>
       </c>
       <c r="P15" t="n">
         <v>126600</v>
